--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_956_Thailand_Andaman_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_956_Thailand_Andaman_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R1fdeec65a3f54fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re18ab05db2f64482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R751538058f254cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8c6886ea22da4e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6a432b86d3d54277"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0879b8d56cd244fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd8a98566a31c4ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R66ebd888b1c6485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8f122d1cf2294073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7daa57f6e2f647f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1c9a1c91c84b4e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R47dbaf2d47e24a3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ956CommercialTable" displayName="EEZ956CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ956CommercialTable" displayName="EEZ956CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ956FunctionalTable" displayName="EEZ956FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ956FunctionalTable" displayName="EEZ956FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ956ValidationTable" displayName="EEZ956ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ956ValidationTable" displayName="EEZ956ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5317,7 +5271,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02789dc568584851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7eec1daa2ff34b58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5327,20 +5281,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5348,606 +5292,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>26768.850256618098</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>26768.850256618098</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$70,A2,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4242576.854172497</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>4242576.854172497</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>12865.9982392464</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.6434447096041587</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>43.99919285275628</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>12865.9982392464</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>94.47555901299572</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$70,A3,'Species'!$U$2:$U$70))</x:f>
-        <x:v>1215522.3759130223</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.6434447096041587</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>43.99919285275628</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>566093.5377718251</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>649428.8381411972</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>2.147211184740572</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.147211184740572</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>98.9329564803</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>98.9329564803</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$70,A4,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>242851.61032727134</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>242851.61032727134</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>13412.398728773</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.914487235078298</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>82.12724133795118</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>13412.398728773</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>213.0723348415385</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$70,A5,'Species'!$U$2:$U$70))</x:f>
-        <x:v>2857811.112965346</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.914487235078298</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>82.12724133795118</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1101523.3073187696</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1756287.8056465762</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.5944172892006945</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.5944172892006945</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>20.842445487800003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>20.842445487800003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$70,A6,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>262.3908426852611</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>262.3908426852611</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>97168.32536104402</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8184312876833744</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>658.3112663570981</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>97168.32536104402</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1024.0945232258134</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$70,A7,'Species'!$U$2:$U$70))</x:f>
-        <x:v>99509549.83326907</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8184312876833744</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>658.3112663570981</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>63967003.31822742</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>35542546.51504166</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5556387617256693</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5556387617256692</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>248517.79553099532</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6790056234882873</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>477.535457014319</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>248517.79553099532</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>680.7992965565749</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$70,A8,'Species'!$U$2:$U$70))</x:f>
-        <x:v>169190740.3792923</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6790056234882873</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>477.535457014319</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>118676059.06508493</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>50514681.314207375</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4256518265954876</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.42565182659548756</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>11267.6608744789</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>11267.6608744789</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$70,A9,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8950221.171896676</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>8950221.171896676</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1840.4362914852</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5574860402163297</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>360.98241012942003</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1840.4362914852</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>422.5838864768285</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$70,A10,'Species'!$U$2:$U$70))</x:f>
-        <x:v>777738.7208688171</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5574860402163297</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>360.98241012942003</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>664365.1281899792</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>113373.59267883783</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1706495236854424</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1706495236854424</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9492.874854833199</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.43894791442154</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2747.5646138607485</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9492.874854833199</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2792.3824123990394</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$70,A11,'Species'!$U$2:$U$70))</x:f>
-        <x:v>26507736.787741307</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.43894791442154</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2747.5646138607485</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>26082287.034948185</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>425449.7527931221</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0163118269583895</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01631182695838955</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e1869c3b2f94200"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e0788c2c4fa4a9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5957,20 +5507,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5978,1092 +5518,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>23657.3787027858</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.849127998180228</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>706.5257555858367</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>23657.3787027858</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>729.6145777104565</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$70,A2,'Species'!$U$2:$U$70))</x:f>
-        <x:v>17260768.37196941</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.849127998180228</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>706.5257555858367</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>16714547.36316602</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>546221.00880339</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0326793778458578</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.032679377845857886</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>11996.7280563814</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>11996.7280563814</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$70,A3,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3459894.1649046773</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3459894.1649046773</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3815.7120045243</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.341864752661937</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2197.175525114958</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3815.7120045243</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2258.992453191862</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$70,A4,'Species'!$U$2:$U$70))</x:f>
-        <x:v>8619664.621773984</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.341864752661937</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2197.175525114958</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>8383789.027228128</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>235875.59454585612</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0281347244998413</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.028134724499841328</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>485.8206725843</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.370559111686938</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2347.248724239315</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>485.8206725843</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2348.446337791329</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$70,A5,'Species'!$U$2:$U$70))</x:f>
-        <x:v>1140923.7793539197</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.370559111686938</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2347.248724239315</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1140341.953932584</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>581.8254213356413</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0005102201311888</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0005102201311888577</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>15317.5157010295</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.433003546654675</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2710.2137646912115</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>15317.5157010295</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2727.4109950831676</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$70,A6,'Species'!$U$2:$U$70))</x:f>
-        <x:v>41777160.740346916</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.433003546654675</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2710.2137646912115</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>41513741.8938039</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>263418.84654301405</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.006345340952807</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.006345340952807013</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1645.4968561658</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.499138682792101</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>315.6012268500911</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1645.4968561658</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>339.7229687036973</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$70,A7,'Species'!$U$2:$U$70))</x:f>
-        <x:v>559013.0769692464</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.499138682792101</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>315.6012268500911</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>519320.8265838944</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>39692.250385352</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0764310775796315</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.07643107757963152</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>194.93943531940002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>194.93943531940002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$70,A8,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>218725.64389957068</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>218725.64389957068</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8404.9153447984</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.5050569152318056</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>31.99314359290139</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8404.9153447984</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>34.459135957055985</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$70,A9,'Species'!$U$2:$U$70))</x:f>
-        <x:v>289626.1205739542</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.5050569152318056</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>31.99314359290139</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>268899.66351231554</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>20726.457061638648</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.077078776488277</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07707877648827693</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>247.59327118789997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.024285301704039</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>105.75119939625996</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>247.59327118789997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>114.2689666910065</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$70,A10,'Species'!$U$2:$U$70))</x:f>
-        <x:v>28292.22725828748</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.024285301704039</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>105.75119939625996</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>26183.285390563877</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2108.9418677236026</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0805453493045467</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.08054534930454672</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>83018.56533638321</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8721289617069914</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>744.9531514056274</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>83018.56533638321</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1126.8522893490765</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$70,A11,'Species'!$U$2:$U$70))</x:f>
-        <x:v>93549660.4077793</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8721289617069914</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>744.9531514056274</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>61844941.87251265</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>31704718.535266653</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.5126485299415893</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.5126485299415893</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>128010.9254968971</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.76745413486224</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>585.401909707137</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>128010.9254968971</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>768.1956577524537</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$70,A12,'Species'!$U$2:$U$70))</x:f>
-        <x:v>98337437.11158922</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.76745413486224</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>585.401909707137</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>74937840.2492616</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>23399596.86232762</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3122534194272857</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3122534194272858</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>21368.897691385202</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.9448311311857354</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>880.7063571283678</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>21368.897691385202</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1048.9514924537905</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$70,A13,'Species'!$U$2:$U$70))</x:f>
-        <x:v>22414937.125470866</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.9448311311857354</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>880.7063571283678</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>18819724.04162865</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>3595213.083842214</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1910343146312727</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.19103431463127266</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>367.72077411419997</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.4112955712726802</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>25.780751413133014</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>367.72077411419997</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>26.10334378868625</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$70,A14,'Species'!$U$2:$U$70))</x:f>
-        <x:v>9598.741784944801</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.4112955712726802</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>25.780751413133014</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>9480.117866883027</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>118.62391806177402</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.012512915949723</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.012512915949722937</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>4461.082894447999</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.9041746094902527</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>80.20004454289551</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>4461.082894447999</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>207.54966389245615</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$70,A15,'Species'!$U$2:$U$70))</x:f>
-        <x:v>925896.2553390677</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.9041746094902527</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>80.20004454289551</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>357779.04684427875</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>568117.208494789</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>2.5878996087271107</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>1.5878996087271111</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>38731.1196075728</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>38731.1196075728</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$70,A16,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>6730697.1752431225</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>6730697.1752431225</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>37784.1448737068</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.5109633745223925</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>324.3122658793213</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>37784.1448737068</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>324.4105610978732</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$70,A17,'Species'!$U$2:$U$70))</x:f>
-        <x:v>12257575.639082551</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.5109633745223925</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>324.3122658793213</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>12253861.638304394</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>3714.000778157264</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0003030881927495</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0003030881927495945</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>38826.059888826</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.0664659726818813</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>116.53757391439065</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>38826.059888826</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>127.55757364191409</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$70,A18,'Species'!$U$2:$U$70))</x:f>
-        <x:v>4952557.993494289</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.0664659726818813</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>116.53757391439065</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>4524694.824098618</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>427863.1693956712</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0945617740044837</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.09456177400448383</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>3020.5659748518</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.3672361864383347</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>232.93577096947382</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>3020.5659748518</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>238.27667931130222</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$70,A19,'Species'!$U$2:$U$70))</x:f>
-        <x:v>719730.4301283933</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.3672361864383347</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>232.93577096947382</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>703597.8641162643</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>16132.566012129071</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0229286739413173</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.02292867394131726</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>98.9329564803</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>98.9329564803</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$70,A20,'Species'!$U$2:$U$70))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>242851.61032727134</x:v>
       </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>242851.61032727134</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R258a988bab4c4fb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87cda4360ffe418b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7238,7 +6069,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7337,7 +6168,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>313495011.237289</x:v>
+        <x:v>224493243.41878027</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7351,7 +6182,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>313495011.23728895</x:v>
+        <x:v>252670912.2626254</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7365,7 +6196,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-89001767.81850868</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7379,7 +6210,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-60824098.974663556</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7390,9 +6221,9 @@
         <x:v>EEZ_956</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7404,47 +6235,19 @@
         <x:v>EEZ_956</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_956</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_956</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red43a78f1eed4402"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11adef783ee4bcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7491,7 +6294,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
